--- a/ig/DM-AVRIL-2026/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
@@ -85,7 +85,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette TRE hiérarchique remplace les TRE_R280-DisciplineEquipementSocial, TRE_R298-AgregatDisciplineEquipSocNiv1, TRE_R299-AgregatDisciplineEquipSocNiv2, TRE_R300-AgregatDisciplineEquipSocNiv3 et l'ASS_X14_AgregatDisciplineEquipementSocial. Cette TRE possède des propriétés spécifiques : le niveau d'agrégat desASOCR de 1 à 4 (du plus large au plus fin), le parent d'un agrégat d'ASOCR ou d'une ASOCR ainsi que les relations nécessaires à la construction des JDV dynamiques associés</t>
+    <t>Cette TRE hiérarchique remplace les éléments suivants :
+TRE_R280-DisciplineEquipementSocial, TRE_R298-AgregatDisciplineEquipSocNiv1, TRE_R299-AgregatDisciplineEquipSocNiv2, TRE_R300-AgregatDisciplineEquipSocNiv3 et ASS_X14_AgregatDisciplineEquipementSocial.
+Cette TRE possède des propriétés spécifiques :
+1. Le niveau d'agrégat des ASOCR de 1 à 4 (du plus large au plus fin)
+2. Le parent d'un agrégat d'ASOCR ou d'une ASOCR
+3. Les relations nécessaires à la construction des JDV dynamiques associés</t>
   </si>
   <si>
     <t>Purpose</t>
